--- a/docs/_baseline/fish_zero_bulk.xlsx
+++ b/docs/_baseline/fish_zero_bulk.xlsx
@@ -5,14 +5,376 @@
     <workbookView activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="어류_입력" state="visible" r:id="rId1"/>
-    <sheet sheetId="2" name="License" state="visible" r:id="rId2"/>
+    <sheet sheetId="1" name="필독" state="visible" r:id="rId1"/>
+    <sheet sheetId="2" name="어류_입력" state="visible" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127">
+  <si>
+    <t>※ 엑셀 기반 수질/생태계 데이터 베이스 작성/관리 시 주의 사항</t>
+  </si>
+  <si>
+    <t>[조사지점] 시트을 확인하고 DB 지점명에 [DB상 지점명] 값으로 입력할 것</t>
+  </si>
+  <si>
+    <t>[어류_입력] 시트 외 자동계산 시트와 계산셀(검은 음영)은 입력 금지</t>
+  </si>
+  <si>
+    <t>[어류_입력] 시트 항목의 주요 내용과 내용 설명을 확인 한 후 예시와 같은 형태로 입력할 것</t>
+  </si>
+  <si>
+    <t>[어류_입력] 시트는 원형을 유지하고 데이터만 입력, 행, 열의 추가 삽입 또는 삭제 금지</t>
+  </si>
+  <si>
+    <t>[어류_입력] 시트 내 항목이 없는 정보 및 특이 사항은 야장(Field note)에 입력</t>
+  </si>
+  <si>
+    <t>[어류_입력] 시트 생물 종, 환경 항목 추가 등 변경 건의 사항이 있을 시, 
+        조사자가 직접 변경하지 않고 과제 담당자에게 요청</t>
+  </si>
+  <si>
+    <t>용역 수행 담당자는 5의 요청된 내용을 취합 하여 발주자(삼성전자)에게 공유</t>
+  </si>
+  <si>
+    <t>발주자는 공유 받은 내용을 반영하여 데이터 프레임 수정 후 재배포</t>
+  </si>
+  <si>
+    <t>주요 내용</t>
+  </si>
+  <si>
+    <t>조사 개황/
+작성 필수</t>
+  </si>
+  <si>
+    <t>채집방법 /
+작성 필수</t>
+  </si>
+  <si>
+    <t>하천차수</t>
+  </si>
+  <si>
+    <t>서식처 /
+가능시 작성</t>
+  </si>
+  <si>
+    <t>채집 불가시 /
+불가시만 입력</t>
+  </si>
+  <si>
+    <t>기입 항목
+아님
+(자동 계산)</t>
+  </si>
+  <si>
+    <t>비정상종 /
+출현시만</t>
+  </si>
+  <si>
+    <t>기입 항목
+아님
+(자동계산)</t>
+  </si>
+  <si>
+    <t>과</t>
+  </si>
+  <si>
+    <t>내용 설명</t>
+  </si>
+  <si>
+    <t>조사 연도/차수 (필수)</t>
+  </si>
+  <si>
+    <t>지점명 (필수)</t>
+  </si>
+  <si>
+    <t>조사일 (필수)</t>
+  </si>
+  <si>
+    <t>대권역명</t>
+  </si>
+  <si>
+    <t>중권역명</t>
+  </si>
+  <si>
+    <t>하천명</t>
+  </si>
+  <si>
+    <t>하천유형</t>
+  </si>
+  <si>
+    <t>조사지점 좌표-위도</t>
+  </si>
+  <si>
+    <t>조사지점 좌표-경도</t>
+  </si>
+  <si>
+    <t>날씨</t>
+  </si>
+  <si>
+    <t>조사기관</t>
+  </si>
+  <si>
+    <t>조사자</t>
+  </si>
+  <si>
+    <t>채집소요시간</t>
+  </si>
+  <si>
+    <t>채집도구</t>
+  </si>
+  <si>
+    <t>흐름상태</t>
+  </si>
+  <si>
+    <t>입력 금지 (자동생성)</t>
+  </si>
+  <si>
+    <t>하상구성</t>
+  </si>
+  <si>
+    <t>하천형태</t>
+  </si>
+  <si>
+    <t xml:space="preserve">채집 불가시 항목 </t>
+  </si>
+  <si>
+    <t>군집정보</t>
+  </si>
+  <si>
+    <t>국내종</t>
+  </si>
+  <si>
+    <t>내성도</t>
+  </si>
+  <si>
+    <t>섭식특성</t>
+  </si>
+  <si>
+    <t>서식지</t>
+  </si>
+  <si>
+    <t>비정상(DB용)</t>
+  </si>
+  <si>
+    <t>모델값(DB용)</t>
+  </si>
+  <si>
+    <t>모델값</t>
+  </si>
+  <si>
+    <t>건강도등급</t>
+  </si>
+  <si>
+    <t>메트릭_백분율</t>
+  </si>
+  <si>
+    <t>통합평가_백분율</t>
+  </si>
+  <si>
+    <t>세부 설명</t>
+  </si>
+  <si>
+    <t>"20XX반기1차" 형태로 작성, 띄어쓰기 없이 
+반기/분기/격월 등 맞춰 표기</t>
+  </si>
+  <si>
+    <t>OO천+숫자 형태, 띄어쓰기 없이</t>
+  </si>
+  <si>
+    <t>조사일(YYMM01)</t>
+  </si>
+  <si>
+    <t>한강, 금강, 낙동강, 영산/섬진강 중 택 1</t>
+  </si>
+  <si>
+    <t>산간형/평지형/강</t>
+  </si>
+  <si>
+    <t>도분초: 37_12_44.11 or 도: 37.2122527</t>
+  </si>
+  <si>
+    <t>도분초: 127_4_17.59 or 도: 127.0715531</t>
+  </si>
+  <si>
+    <t>1 맑음, 2 흐림, 3 비(눈)</t>
+  </si>
+  <si>
+    <t>기관명</t>
+  </si>
+  <si>
+    <t>성명</t>
+  </si>
+  <si>
+    <t>채집소요시간(분)</t>
+  </si>
+  <si>
+    <t>1 투망/족대, 그외 도구는 도구명 (복수 가능)</t>
+  </si>
+  <si>
+    <t>1 여울, 2 흐름, 3 소 (복수 가능)</t>
+  </si>
+  <si>
+    <t>하천차수 (지점마다 고정값, 사업 담당자 문의)</t>
+  </si>
+  <si>
+    <t>암반</t>
+  </si>
+  <si>
+    <t>콘크리트</t>
+  </si>
+  <si>
+    <t>진흙이하(&lt;0.063mm)</t>
+  </si>
+  <si>
+    <t>모래(0.063-2mm)</t>
+  </si>
+  <si>
+    <t>잔자갈(2-16mm)</t>
+  </si>
+  <si>
+    <t>자갈(16-64mm)</t>
+  </si>
+  <si>
+    <t>작은돌(64-256mm)</t>
+  </si>
+  <si>
+    <t>큰돌(&gt;256mm)</t>
+  </si>
+  <si>
+    <t>% 총합 확인(100%)</t>
+  </si>
+  <si>
+    <t>1(자연형), 2(직강화), 3(복합형), 4(댐/보/교각), 5(공사)</t>
+  </si>
+  <si>
+    <t>1(아주빠름), 2(빠름), 3(보통), 4(느림), 5(정체)</t>
+  </si>
+  <si>
+    <t>특이사항(접근불가, 건천화, 공사중, 준설 中 선택)</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>총 개체수(어류특성미확정종포함)</t>
+  </si>
+  <si>
+    <t>총 종수(어류특성미확정종포함)</t>
+  </si>
+  <si>
+    <t>총 개체수</t>
+  </si>
+  <si>
+    <t>총 종수</t>
+  </si>
+  <si>
+    <t>국내종총종수</t>
+  </si>
+  <si>
+    <t>여울성저서종수</t>
+  </si>
+  <si>
+    <t>민감종수</t>
+  </si>
+  <si>
+    <t>내성종개체수비율 (%)</t>
+  </si>
+  <si>
+    <t>잡식종개체수비율 (%)</t>
+  </si>
+  <si>
+    <t>충식종개체수비율 (%)</t>
+  </si>
+  <si>
+    <t>국내종총개체수</t>
+  </si>
+  <si>
+    <t>비정상개체수(총합)</t>
+  </si>
+  <si>
+    <t>기형(deformity) DE 종명(개체수)</t>
+  </si>
+  <si>
+    <t>지느러미손상(erosion of fin) EF 종명(개체수)</t>
+  </si>
+  <si>
+    <t>피부손상(lesions) LE 종명(개체수)</t>
+  </si>
+  <si>
+    <t>종양(tumors) TU 종명(개체수)</t>
+  </si>
+  <si>
+    <t>비정상개체수비율 (%)</t>
+  </si>
+  <si>
+    <t>M1 (국내종의 총 종수)</t>
+  </si>
+  <si>
+    <t>M2 (여울성 저서종수)</t>
+  </si>
+  <si>
+    <t>M3 (민감종수)</t>
+  </si>
+  <si>
+    <t>M4 (내성종의 개체수 비율)</t>
+  </si>
+  <si>
+    <t>M5 (잡식종의 개체수 비율)</t>
+  </si>
+  <si>
+    <t>M6 (국내종의 충식종 개체수 비율)</t>
+  </si>
+  <si>
+    <t>M7 (채집된 국내종의 총 개체수)</t>
+  </si>
+  <si>
+    <t>M8 (비정상종의 개체수 비율)</t>
+  </si>
+  <si>
+    <t>메트릭모델값</t>
+  </si>
+  <si>
+    <t>등급(A - D)</t>
+  </si>
+  <si>
+    <t>메트릭모델값(특이사항 반영)</t>
+  </si>
+  <si>
+    <t>2020 FAI 등급(A - E)</t>
+  </si>
+  <si>
+    <t>(예시)</t>
+  </si>
+  <si>
+    <t>2023분기1차</t>
+  </si>
+  <si>
+    <t>삼성천1(예시)</t>
+  </si>
+  <si>
+    <t>한강</t>
+  </si>
+  <si>
+    <t>안성천</t>
+  </si>
+  <si>
+    <t>오산천</t>
+  </si>
+  <si>
+    <t>평지형</t>
+  </si>
+  <si>
+    <t>삼성전자</t>
+  </si>
+  <si>
+    <t>김삼성</t>
+  </si>
+  <si>
+    <t>1,3</t>
+  </si>
   <si>
     <t>2026반기1차_0종</t>
   </si>
@@ -29,9 +391,6 @@
     <t>곡교천</t>
   </si>
   <si>
-    <t>평지형</t>
-  </si>
-  <si>
     <t>맑음</t>
   </si>
   <si>
@@ -45,9 +404,6 @@
   </si>
   <si>
     <t>출현종 없음(0종) 선언</t>
-  </si>
-  <si>
-    <t>Thank you for using version 2026.2.519.80 of Telerik Document Processing Libraries. License validation couldn't run, possibly due to a missing Telerik.Licensing NuGet package reference to BaselineGen. See documentation for setup. Learn more about Telerik Document Processing Libraries licensing https://docs.telerik.com/devtools/document-processing/distribution-and-licensing/license-key</t>
   </si>
 </sst>
 </file>
@@ -55,22 +411,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <b val="false"/>
       <i val="false"/>
       <u val="none"/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="false"/>
-      <i val="false"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -94,9 +441,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
-    <xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -216,82 +562,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="Q2" t="s">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="Q3" t="s">
+    <row r="4">
+      <c r="B4" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="Q4" t="n">
-        <v>20260514</v>
+      <c r="C4" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="Q5" t="s">
+      <c r="B5" t="n">
         <v>2</v>
       </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
-      <c r="Q6" t="s">
+      <c r="B6" t="n">
         <v>3</v>
       </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
-      <c r="Q7" t="s">
+      <c r="B7" t="n">
         <v>4</v>
       </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
-      <c r="Q8" t="s">
+      <c r="B8" t="n">
         <v>5</v>
       </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
-      <c r="Q9" t="n">
-        <v>36.763081</v>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="n">
-        <v>127.090606</v>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="Q12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="Q13" t="s">
+      <c r="B11" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="Q15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="Q30" t="s">
-        <v>10</v>
+      <c r="C11" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -301,12 +641,643 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="M2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="N3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="N4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P4" t="n">
+        <v>230309</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>20260514</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="N5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
+        <v>54</v>
+      </c>
+      <c r="P5" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="N6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="N8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" t="s">
+        <v>55</v>
+      </c>
+      <c r="P8" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="N9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P9" t="n">
+        <v>37.2122527</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>36.763081</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="N10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P10" t="n">
+        <v>127.0715531</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>127.090606</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" t="s">
+        <v>58</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="N12" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" t="s">
+        <v>59</v>
+      </c>
+      <c r="P12" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="N13" t="s">
+        <v>31</v>
+      </c>
+      <c r="O13" t="s">
+        <v>60</v>
+      </c>
+      <c r="P13" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="M14" t="s">
         <v>11</v>
+      </c>
+      <c r="N14" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" t="s">
+        <v>61</v>
+      </c>
+      <c r="P14" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="N15" t="s">
+        <v>33</v>
+      </c>
+      <c r="O15" t="s">
+        <v>62</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="N16" t="s">
+        <v>34</v>
+      </c>
+      <c r="O16" t="s">
+        <v>63</v>
+      </c>
+      <c r="P16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="M17" t="s">
+        <v>12</v>
+      </c>
+      <c r="N17" t="s">
+        <v>35</v>
+      </c>
+      <c r="O17" t="s">
+        <v>64</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="M18" t="s">
+        <v>13</v>
+      </c>
+      <c r="N18" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="O19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="O20" t="s">
+        <v>67</v>
+      </c>
+      <c r="P20" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="O21" t="s">
+        <v>68</v>
+      </c>
+      <c r="P21" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="O22" t="s">
+        <v>69</v>
+      </c>
+      <c r="P22" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="O23" t="s">
+        <v>70</v>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="O24" t="s">
+        <v>71</v>
+      </c>
+      <c r="P24" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="O25" t="s">
+        <v>72</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="N26" t="s">
+        <v>35</v>
+      </c>
+      <c r="O26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>74</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="N28" t="s">
+        <v>34</v>
+      </c>
+      <c r="O28" t="s">
+        <v>75</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="M29" t="s">
+        <v>14</v>
+      </c>
+      <c r="N29" t="s">
+        <v>38</v>
+      </c>
+      <c r="O29" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="O30" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="M31" t="s">
+        <v>15</v>
+      </c>
+      <c r="N31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="O32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="O33" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="O34" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="O35" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="N36" t="s">
+        <v>40</v>
+      </c>
+      <c r="O36" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="O37" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="N38" t="s">
+        <v>41</v>
+      </c>
+      <c r="O38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="O39" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="N40" t="s">
+        <v>42</v>
+      </c>
+      <c r="O40" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="O41" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="N42" t="s">
+        <v>43</v>
+      </c>
+      <c r="O42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="M43" t="s">
+        <v>16</v>
+      </c>
+      <c r="N43" t="s">
+        <v>44</v>
+      </c>
+      <c r="O43" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="O44" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="O45" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="O46" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="O47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" t="s">
+        <v>44</v>
+      </c>
+      <c r="O48" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="O49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="O50" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="O51" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="O52" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="O53" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="O54" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="O55" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="O56" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="N57" t="s">
+        <v>45</v>
+      </c>
+      <c r="O57" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="N58" t="s">
+        <v>46</v>
+      </c>
+      <c r="O58" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="N59" t="s">
+        <v>47</v>
+      </c>
+      <c r="O59" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="N60" t="s">
+        <v>48</v>
+      </c>
+      <c r="O60" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="O61" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="O62" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="O63" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="O64" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="O65" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="O66" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="O67" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="N68" t="s">
+        <v>49</v>
+      </c>
+      <c r="O68" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="O69" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="O70" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="O71" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="O72" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="O73" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="O74" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="O75" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="N76" t="s">
+        <v>49</v>
+      </c>
+      <c r="O76" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="O77" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="M78" t="s">
+        <v>18</v>
+      </c>
+      <c r="O78" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
